--- a/artfynd/A 62537-2023 artfynd.xlsx
+++ b/artfynd/A 62537-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62537-2023 artfynd.xlsx
+++ b/artfynd/A 62537-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>121016193</v>
       </c>
       <c r="B3" t="n">
-        <v>103585</v>
+        <v>103595</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62537-2023 artfynd.xlsx
+++ b/artfynd/A 62537-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>121016193</v>
       </c>
       <c r="B3" t="n">
-        <v>103595</v>
+        <v>103608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62537-2023 artfynd.xlsx
+++ b/artfynd/A 62537-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109191003</v>
+        <v>121016193</v>
       </c>
       <c r="B2" t="n">
-        <v>97911</v>
+        <v>104707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224361</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300 m N-NNV om Klintens topp, Nb</t>
+          <t>Klinten 250 m NNV om högsta punkten, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-04</t>
+          <t>1997-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-04</t>
+          <t>1997-06-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Norrbottens flora - 2010. Belägg hos Lennart Stenberg.</t>
+          <t>Norrbottens flora - 2010.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,17 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>grustag med skalgrus, igenväxt med lövskog</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>nb99 2687</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Lennart Stenberg</t>
+          <t>rik granskogssluttning på skalgrus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121016193</v>
+        <v>109191003</v>
       </c>
       <c r="B3" t="n">
-        <v>104562</v>
+        <v>98052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,27 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>224361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klinten 250 m NNV om högsta punkten, Nb</t>
+          <t>300 m N-NNV om Klintens topp, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -861,17 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-06-22</t>
+          <t>2000-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-06-22</t>
+          <t>2000-06-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Norrbottens flora - 2010.</t>
+          <t>Norrbottens flora - 2010. Belägg hos Lennart Stenberg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +875,17 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>rik granskogssluttning på skalgrus</t>
+          <t>grustag med skalgrus, igenväxt med lövskog</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>nb99 2687</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
